--- a/docs/page-copy/07-我们的成就.xlsx
+++ b/docs/page-copy/07-我们的成就.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G132"/>
+  <dimension ref="A1:G158"/>
   <cols>
     <col min="1" max="1" width="36.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
@@ -453,7 +453,7 @@
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="3">
@@ -476,7 +476,7 @@
         <v/>
       </c>
       <c r="G3" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="4">
@@ -499,7 +499,7 @@
         <v/>
       </c>
       <c r="G4" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="5">
@@ -522,7 +522,7 @@
         <v/>
       </c>
       <c r="G5" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="6">
@@ -545,7 +545,7 @@
         <v/>
       </c>
       <c r="G6" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="7">
@@ -568,7 +568,7 @@
         <v/>
       </c>
       <c r="G7" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="8">
@@ -591,7 +591,7 @@
         <v/>
       </c>
       <c r="G8" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="9">
@@ -614,7 +614,7 @@
         <v/>
       </c>
       <c r="G9" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="10">
@@ -637,7 +637,7 @@
         <v/>
       </c>
       <c r="G10" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="11">
@@ -660,7 +660,7 @@
         <v/>
       </c>
       <c r="G11" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="12">
@@ -683,7 +683,7 @@
         <v/>
       </c>
       <c r="G12" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="13" xml:space="preserve">
@@ -708,7 +708,7 @@
         <v/>
       </c>
       <c r="G13" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="14">
@@ -731,7 +731,7 @@
         <v/>
       </c>
       <c r="G14" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="15">
@@ -754,7 +754,7 @@
         <v/>
       </c>
       <c r="G15" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="16" xml:space="preserve">
@@ -779,7 +779,7 @@
         <v/>
       </c>
       <c r="G16" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="17">
@@ -802,7 +802,7 @@
         <v/>
       </c>
       <c r="G17" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="18">
@@ -825,7 +825,7 @@
         <v/>
       </c>
       <c r="G18" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="19" xml:space="preserve">
@@ -850,7 +850,7 @@
         <v/>
       </c>
       <c r="G19" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="20">
@@ -873,7 +873,7 @@
         <v/>
       </c>
       <c r="G20" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="21">
@@ -896,7 +896,7 @@
         <v/>
       </c>
       <c r="G21" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="22">
@@ -919,7 +919,7 @@
         <v/>
       </c>
       <c r="G22" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="23">
@@ -942,7 +942,7 @@
         <v/>
       </c>
       <c r="G23" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="24">
@@ -965,7 +965,7 @@
         <v/>
       </c>
       <c r="G24" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="25">
@@ -988,7 +988,7 @@
         <v/>
       </c>
       <c r="G25" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="26">
@@ -1011,7 +1011,7 @@
         <v/>
       </c>
       <c r="G26" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="27">
@@ -1034,7 +1034,7 @@
         <v/>
       </c>
       <c r="G27" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="28">
@@ -1057,7 +1057,7 @@
         <v/>
       </c>
       <c r="G28" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="29">
@@ -1080,7 +1080,7 @@
         <v/>
       </c>
       <c r="G29" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="30">
@@ -1103,7 +1103,7 @@
         <v/>
       </c>
       <c r="G30" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="31">
@@ -1126,7 +1126,7 @@
         <v/>
       </c>
       <c r="G31" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="32">
@@ -1149,7 +1149,7 @@
         <v/>
       </c>
       <c r="G32" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="33">
@@ -1172,7 +1172,7 @@
         <v/>
       </c>
       <c r="G33" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="34">
@@ -1195,7 +1195,7 @@
         <v/>
       </c>
       <c r="G34" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="35">
@@ -1218,7 +1218,7 @@
         <v/>
       </c>
       <c r="G35" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         <v/>
       </c>
       <c r="G36" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="37">
@@ -1264,7 +1264,7 @@
         <v/>
       </c>
       <c r="G37" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="38">
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="G38" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="39">
@@ -1310,7 +1310,7 @@
         <v/>
       </c>
       <c r="G39" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="40">
@@ -1333,7 +1333,7 @@
         <v/>
       </c>
       <c r="G40" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="41">
@@ -1356,7 +1356,7 @@
         <v/>
       </c>
       <c r="G41" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="42">
@@ -1379,7 +1379,7 @@
         <v/>
       </c>
       <c r="G42" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="43">
@@ -1402,7 +1402,7 @@
         <v/>
       </c>
       <c r="G43" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="44">
@@ -1425,7 +1425,7 @@
         <v/>
       </c>
       <c r="G44" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="45">
@@ -1448,7 +1448,7 @@
         <v/>
       </c>
       <c r="G45" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="46">
@@ -1471,7 +1471,7 @@
         <v/>
       </c>
       <c r="G46" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="47">
@@ -1494,7 +1494,7 @@
         <v/>
       </c>
       <c r="G47" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="48">
@@ -1517,7 +1517,7 @@
         <v/>
       </c>
       <c r="G48" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="49">
@@ -1540,7 +1540,7 @@
         <v/>
       </c>
       <c r="G49" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="50">
@@ -1563,7 +1563,7 @@
         <v/>
       </c>
       <c r="G50" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="51">
@@ -1586,7 +1586,7 @@
         <v/>
       </c>
       <c r="G51" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="52">
@@ -1609,7 +1609,7 @@
         <v/>
       </c>
       <c r="G52" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="53" xml:space="preserve">
@@ -1634,7 +1634,7 @@
         <v/>
       </c>
       <c r="G53" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="54">
@@ -1657,7 +1657,7 @@
         <v/>
       </c>
       <c r="G54" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="55" xml:space="preserve">
@@ -1682,7 +1682,7 @@
         <v/>
       </c>
       <c r="G55" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="56">
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="G56" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="57" xml:space="preserve">
@@ -1730,7 +1730,7 @@
         <v/>
       </c>
       <c r="G57" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="58">
@@ -1753,7 +1753,7 @@
         <v/>
       </c>
       <c r="G58" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="59">
@@ -1776,7 +1776,7 @@
         <v/>
       </c>
       <c r="G59" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="60">
@@ -1799,7 +1799,7 @@
         <v/>
       </c>
       <c r="G60" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="61">
@@ -1822,7 +1822,7 @@
         <v/>
       </c>
       <c r="G61" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="62">
@@ -1845,7 +1845,7 @@
         <v/>
       </c>
       <c r="G62" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="63">
@@ -1868,7 +1868,7 @@
         <v/>
       </c>
       <c r="G63" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="64">
@@ -1891,7 +1891,7 @@
         <v/>
       </c>
       <c r="G64" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="65">
@@ -1914,7 +1914,7 @@
         <v/>
       </c>
       <c r="G65" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="66">
@@ -1937,7 +1937,7 @@
         <v/>
       </c>
       <c r="G66" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="67">
@@ -1960,7 +1960,7 @@
         <v/>
       </c>
       <c r="G67" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="68">
@@ -1983,7 +1983,7 @@
         <v/>
       </c>
       <c r="G68" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="69">
@@ -2006,7 +2006,7 @@
         <v/>
       </c>
       <c r="G69" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="70">
@@ -2029,7 +2029,7 @@
         <v/>
       </c>
       <c r="G70" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="71">
@@ -2052,7 +2052,7 @@
         <v/>
       </c>
       <c r="G71" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="72">
@@ -2075,7 +2075,7 @@
         <v/>
       </c>
       <c r="G72" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="73">
@@ -2098,7 +2098,7 @@
         <v/>
       </c>
       <c r="G73" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="74">
@@ -2121,7 +2121,7 @@
         <v/>
       </c>
       <c r="G74" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="75">
@@ -2144,7 +2144,7 @@
         <v/>
       </c>
       <c r="G75" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="76">
@@ -2167,7 +2167,7 @@
         <v/>
       </c>
       <c r="G76" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="77">
@@ -2190,7 +2190,7 @@
         <v/>
       </c>
       <c r="G77" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="78">
@@ -2213,7 +2213,7 @@
         <v/>
       </c>
       <c r="G78" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="79">
@@ -2236,7 +2236,7 @@
         <v/>
       </c>
       <c r="G79" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="80">
@@ -2259,7 +2259,7 @@
         <v/>
       </c>
       <c r="G80" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="81">
@@ -2282,7 +2282,7 @@
         <v/>
       </c>
       <c r="G81" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="82">
@@ -2305,7 +2305,7 @@
         <v/>
       </c>
       <c r="G82" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="83">
@@ -2328,7 +2328,7 @@
         <v/>
       </c>
       <c r="G83" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="84">
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="G84" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="85">
@@ -2374,7 +2374,7 @@
         <v/>
       </c>
       <c r="G85" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="86">
@@ -2397,7 +2397,7 @@
         <v/>
       </c>
       <c r="G86" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="87">
@@ -2420,1047 +2420,1645 @@
         <v/>
       </c>
       <c r="G87" t="str">
-        <v>achievementsReport.i18n.ts</v>
+        <v>achievementsReport.i18n.ts — matches translate() merge on site</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>achievementsPage.backHome</v>
+        <v>home.achievements.card1Body</v>
       </c>
       <c r="B88" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>首页 / 成就摘要条（链到专页）</v>
       </c>
       <c r="C88" t="str">
         <v>paragraph / other</v>
       </c>
       <c r="D88" t="str">
-        <v>← Back to Home</v>
+        <v>255+ documented public-benefit sessions; 800+ broadcast hours; an estimated 70,000+ platform-indicated listener contacts; 1,200+ extended interviews; 240+ individuals reporting improvement in mental-health–related distress; approximately 400 distinct attached spirits noted in records (some hosts carried multiples). Structured replays are archived on YouTube.</v>
       </c>
       <c r="E88" t="str">
-        <v>← 返回首页</v>
+        <v>265+ 场有记录的公益直播；800+ 播出小时；约 70,000+ 次平台显示的触达；1,200+ 次延展访谈；240+ 名自述精神健康痛苦减轻者；约 400 个在记录中出现的附体灵体（部分宿主报告多重）。结构化回放存档于 YouTube。</v>
       </c>
       <c r="F88" t="str">
         <v/>
       </c>
       <c r="G88" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>; HomeView → components/home/Achievements.tsx</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>achievementsPage.banner.together</v>
+        <v>home.achievements.card1Title</v>
       </c>
       <c r="B89" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>首页 / 成就摘要条（链到专页）</v>
       </c>
       <c r="C89" t="str">
-        <v>paragraph / other</v>
+        <v>heading</v>
       </c>
       <c r="D89" t="str">
-        <v>Behind every figure is a real person seeking relief — and a community of practitioners holding space for change.</v>
+        <v>Data overview</v>
       </c>
       <c r="E89" t="str">
-        <v>每个数字背后都是在寻求缓解的真实的人——以及为改变托住空间的社群。</v>
+        <v>规模（一年）</v>
       </c>
       <c r="F89" t="str">
         <v/>
       </c>
       <c r="G89" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>; HomeView → components/home/Achievements.tsx</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>achievementsPage.case.cult.body</v>
+        <v>home.achievements.card2Body</v>
       </c>
       <c r="B90" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>首页 / 成就摘要条（链到专页）</v>
       </c>
       <c r="C90" t="str">
         <v>paragraph / other</v>
       </c>
       <c r="D90" t="str">
-        <v>An individual exiting coercive group influence and medium-channel imprinting. Intervention targeted residual cultic and “spirit-medium” attachments described as negative spiritual load; subjective clearance of those influences was reported.</v>
+        <v>Here displays: lived state of American spirits (ghosts), especially notable spirits (ghosts), Master Spirit appearances in the livestream, routine mental-disorder spirit (ghost) management report, special illustrative spirit (ghost) regulation cases</v>
       </c>
       <c r="E90" t="str">
-        <v>脱离强制性团体影响与灵媒印痕者。干预针对残留的邪教式与“灵媒”附体，描述为负面灵性负荷；报告称主观上已清除。</v>
+        <v>专页包含：灵体基线访谈的综合、示范性附体叙事、按时间摘录的场次、非穷尽症状列表、队列来源与流程、两种主要技术路径、参与者自述转归、会话内结构化观察，以及四例匿名案例摘要。</v>
       </c>
       <c r="F90" t="str">
         <v/>
       </c>
       <c r="G90" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>; HomeView → components/home/Achievements.tsx</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>achievementsPage.case.cult.title</v>
+        <v>home.achievements.card2Title</v>
       </c>
       <c r="B91" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>首页 / 成就摘要条（链到专页）</v>
       </c>
       <c r="C91" t="str">
         <v>heading</v>
       </c>
       <c r="D91" t="str">
-        <v>Survivor of high-control ideological abuse</v>
+        <v>Content</v>
       </c>
       <c r="E91" t="str">
-        <v>高控制意识形态虐待幸存者</v>
+        <v>长文档说明</v>
       </c>
       <c r="F91" t="str">
         <v/>
       </c>
       <c r="G91" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>; HomeView → components/home/Achievements.tsx</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>achievementsPage.case.depression.body</v>
+        <v>home.achievements.cta</v>
       </c>
       <c r="B92" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>首页 / 成就摘要条（链到专页）</v>
       </c>
       <c r="C92" t="str">
-        <v>paragraph / other</v>
+        <v>button / link</v>
       </c>
       <c r="D92" t="str">
-        <v>Long-standing depressive illness without durable relief from conventional routes. A single 30-minute intensive session was associated with reported remission-like relief of mood and energy, with stability maintained afterward without relapse.</v>
+        <v>View full documentation</v>
       </c>
       <c r="E92" t="str">
-        <v>长年抑郁，常规路径未见持久缓解。单次 30 分钟强化会话后，报告称情绪与精力呈缓解样改善，此后保持稳定、无复发报告。</v>
+        <v>查看完整文档</v>
       </c>
       <c r="F92" t="str">
         <v/>
       </c>
       <c r="G92" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>; HomeView → components/home/Achievements.tsx</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>achievementsPage.case.depression.title</v>
+        <v>home.achievements.ctaIntro</v>
       </c>
       <c r="B93" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>首页 / 成就摘要条（链到专页）</v>
       </c>
       <c r="C93" t="str">
-        <v>heading</v>
+        <v>button / link</v>
       </c>
       <c r="D93" t="str">
-        <v>Treatment-resistant depression (&gt;40 years)</v>
+        <v>Continue to the full report for tabulated metrics, qualitative findings, methodology notes, and case narratives.</v>
       </c>
       <c r="E93" t="str">
-        <v>难治性抑郁（&gt;40 年）</v>
+        <v>完整报告载有分项数据、质性发现、方法说明与案例叙述。</v>
       </c>
       <c r="F93" t="str">
         <v/>
       </c>
       <c r="G93" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>; HomeView → components/home/Achievements.tsx</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>achievementsPage.case.did.body</v>
+        <v>home.achievements.kickerDoc</v>
       </c>
       <c r="B94" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>首页 / 成就摘要条（链到专页）</v>
       </c>
       <c r="C94" t="str">
-        <v>paragraph / other</v>
+        <v>label</v>
       </c>
       <c r="D94" t="str">
-        <v>A woman with severe dissociative fragmentation (more than thirty distinct identity facets reported). After systematic regulation and internal harmonization, all facets were described as co-existing cooperatively; host-level distress and switching burden were substantially reduced.</v>
+        <v>Field documentation</v>
       </c>
       <c r="E94" t="str">
-        <v>一名严重分离碎裂的女性（报告三十余个不同身份面向）。经系统调节与内部整合后，各面向被描述为合作共存；宿主痛苦与切换负担显著减轻。</v>
+        <v>田野记录</v>
       </c>
       <c r="F94" t="str">
         <v/>
       </c>
       <c r="G94" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>; HomeView → components/home/Achievements.tsx</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>achievementsPage.case.did.title</v>
+        <v>home.achievements.kickerMetrics</v>
       </c>
       <c r="B95" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>首页 / 成就摘要条（链到专页）</v>
       </c>
       <c r="C95" t="str">
-        <v>heading</v>
+        <v>label</v>
       </c>
       <c r="D95" t="str">
-        <v>DID — 30+ reported identity facets</v>
+        <v>Session-derived indicators</v>
       </c>
       <c r="E95" t="str">
-        <v>DID — 报告 30+ 身份面向</v>
+        <v>由会话整理的指标</v>
       </c>
       <c r="F95" t="str">
         <v/>
       </c>
       <c r="G95" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>; HomeView → components/home/Achievements.tsx</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>achievementsPage.case.psychosis.body</v>
+        <v>home.achievements.lead</v>
       </c>
       <c r="B96" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>首页 / 成就摘要条（链到专页）</v>
       </c>
       <c r="C96" t="str">
         <v>paragraph / other</v>
       </c>
       <c r="D96" t="str">
-        <v>A malignant alter / possessory pattern reportedly directing major life decisions. Across roughly one month of layered suppression protocol, the intrusive entity influence was heavily dampened; positive and negative symptoms were reported to fall to a manageable baseline.</v>
+        <v>Coordinated with Master Spirit teams, the founder yielded descriptive statistics and qualitative observations on American attached spirits and rescued large-scale treatment-resistant mental-health cases.</v>
       </c>
       <c r="E96" t="str">
-        <v>报告称恶意他我 / 附体模式主导重大人生决定。约一个月分层抑制后，侵扰性灵体影响大幅减弱；阳性与阴性症状回落至可管理基线。</v>
+        <v>在与中美高级灵体团队协同的匿名 TikTok 直播场次中，我们整理出描述性统计与质性材料，涉及美国附体灵体及难治性精神健康主诉。资料与回放用于透明公开；本工作不宣称等同于随机对照临床试验。</v>
       </c>
       <c r="F96" t="str">
         <v/>
       </c>
       <c r="G96" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>; HomeView → components/home/Achievements.tsx</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>achievementsPage.case.psychosis.title</v>
+        <v>home.achievements.subtitle</v>
       </c>
       <c r="B97" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>首页 / 成就摘要条（链到专页）</v>
       </c>
       <c r="C97" t="str">
         <v>heading</v>
       </c>
       <c r="D97" t="str">
-        <v>Severe schizophrenia with possessory steering</v>
+        <v>TikTok Live · YouTube archive · ASRA</v>
       </c>
       <c r="E97" t="str">
-        <v>重度分裂症伴附体操控</v>
+        <v>TikTok 直播 · YouTube 存档 · ASra</v>
       </c>
       <c r="F97" t="str">
         <v/>
       </c>
       <c r="G97" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>; HomeView → components/home/Achievements.tsx</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>achievementsPage.case.ptsd.body</v>
+        <v>home.achievements.title</v>
       </c>
       <c r="B98" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>首页 / 成就摘要条（链到专页）</v>
       </c>
       <c r="C98" t="str">
-        <v>paragraph / other</v>
+        <v>heading</v>
       </c>
       <c r="D98" t="str">
-        <v>Decades-long trauma imprint and hypervigilance. One focused regulatory session was described as fully processing the traumatic residue; the participant reported that the trauma “no longer occupied” their lived experience.</v>
+        <v>Achievements</v>
       </c>
       <c r="E98" t="str">
-        <v>数十年创伤印痕与过度警觉。一次聚焦调节会话后，参与者称创伤残留已“不再占据”其生活体验。</v>
+        <v>2025 年度工作摘要</v>
       </c>
       <c r="F98" t="str">
         <v/>
       </c>
       <c r="G98" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>; HomeView → components/home/Achievements.tsx</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>achievementsPage.case.ptsd.title</v>
+        <v>achievementsPage.backHome</v>
       </c>
       <c r="B99" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C99" t="str">
-        <v>heading</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D99" t="str">
-        <v>Complex PTSD (&gt;33 years)</v>
+        <v>← Back to Home</v>
       </c>
       <c r="E99" t="str">
-        <v>复杂性 PTSD（&gt;33 年）</v>
+        <v>← 返回首页</v>
       </c>
       <c r="F99" t="str">
         <v/>
       </c>
       <c r="G99" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>achievementsPage.case.somatization.body</v>
+        <v>achievementsPage.banner.together</v>
       </c>
       <c r="B100" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C100" t="str">
         <v>paragraph / other</v>
       </c>
       <c r="D100" t="str">
-        <v>Frequent anomalous activity in the home environment together with intense somatic symptom clusters. Field-level cleansing and attachment suppression paralleled a large reduction in bodily distress and functional limitation.</v>
+        <v>Behind every figure is a real person seeking relief — and a community of practitioners holding space for change.</v>
       </c>
       <c r="E100" t="str">
-        <v>家中频繁异象伴随强烈躯体症状群。场域级清理与附体抑制并行，身体痛苦与功能受限显著减轻。</v>
+        <v>每个数字背后都是在寻求缓解的真实的人——以及为改变托住空间的社群。</v>
       </c>
       <c r="F100" t="str">
         <v/>
       </c>
       <c r="G100" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>achievementsPage.case.somatization.title</v>
+        <v>achievementsPage.case.cult.body</v>
       </c>
       <c r="B101" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C101" t="str">
-        <v>heading</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D101" t="str">
-        <v>Residential field disturbance + severe somatization</v>
+        <v>An individual exiting coercive group influence and medium-channel imprinting. Intervention targeted residual cultic and “spirit-medium” attachments described as negative spiritual load; subjective clearance of those influences was reported.</v>
       </c>
       <c r="E101" t="str">
-        <v>住宅场域扰动 + 严重躯体化</v>
+        <v>脱离强制性团体影响与灵媒印痕者。干预针对残留的邪教式与“灵媒”附体，描述为负面灵性负荷；报告称主观上已清除。</v>
       </c>
       <c r="F101" t="str">
         <v/>
       </c>
       <c r="G101" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>achievementsPage.cases.note</v>
+        <v>achievementsPage.case.cult.title</v>
       </c>
       <c r="B102" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C102" t="str">
-        <v>paragraph / other</v>
+        <v>heading</v>
       </c>
       <c r="D102" t="str">
-        <v>Condensed, anonymized summaries for readability; identifiers and timelines adjusted to protect privacy.</v>
+        <v>Survivor of high-control ideological abuse</v>
       </c>
       <c r="E102" t="str">
-        <v>为可读性压缩的匿名摘要；识别信息与时间线已调整以保护隐私。</v>
+        <v>高控制意识形态虐待幸存者</v>
       </c>
       <c r="F102" t="str">
         <v/>
       </c>
       <c r="G102" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>achievementsPage.cases.title</v>
+        <v>achievementsPage.case.depression.body</v>
       </c>
       <c r="B103" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C103" t="str">
-        <v>heading</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D103" t="str">
-        <v>Highlighted case narratives</v>
+        <v>Long-standing depressive illness without durable relief from conventional routes. A single 30-minute intensive session was associated with reported remission-like relief of mood and energy, with stability maintained afterward without relapse.</v>
       </c>
       <c r="E103" t="str">
-        <v>重点案例叙事</v>
+        <v>长年抑郁，常规路径未见持久缓解。单次 30 分钟强化会话后，报告称情绪与精力呈缓解样改善，此后保持稳定、无复发报告。</v>
       </c>
       <c r="F103" t="str">
         <v/>
       </c>
       <c r="G103" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>achievementsPage.closing.body</v>
+        <v>achievementsPage.case.depression.title</v>
       </c>
       <c r="B104" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C104" t="str">
-        <v>paragraph / other</v>
+        <v>heading</v>
       </c>
       <c r="D104" t="str">
-        <v>The material above is a structured excerpt from a larger field record maintained by the Spirit Ambassador Association (ASra).</v>
+        <v>Treatment-resistant depression (&gt;40 years)</v>
       </c>
       <c r="E104" t="str">
-        <v>上文为灵界大使协会（ASra）所保存之较大田野档案的结构化节选。</v>
+        <v>难治性抑郁（&gt;40 年）</v>
       </c>
       <c r="F104" t="str">
         <v/>
       </c>
       <c r="G104" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>achievementsPage.closing.body2</v>
+        <v>achievementsPage.case.did.body</v>
       </c>
       <c r="B105" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C105" t="str">
         <v>paragraph / other</v>
       </c>
       <c r="D105" t="str">
-        <v>Membership and public channels offer routes for inquiry, collaboration, and continued access to session archives as they are published.</v>
+        <v>A woman with severe dissociative fragmentation (more than thirty distinct identity facets reported). After systematic regulation and internal harmonization, all facets were described as co-existing cooperatively; host-level distress and switching burden were substantially reduced.</v>
       </c>
       <c r="E105" t="str">
-        <v>会员与公开渠道提供咨询、协作及在发布后继续获取会话存档的途径。</v>
+        <v>一名严重分离碎裂的女性（报告三十余个不同身份面向）。经系统调节与内部整合后，各面向被描述为合作共存；宿主痛苦与切换负担显著减轻。</v>
       </c>
       <c r="F105" t="str">
         <v/>
       </c>
       <c r="G105" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>achievementsPage.closing.title</v>
+        <v>achievementsPage.case.did.title</v>
       </c>
       <c r="B106" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C106" t="str">
         <v>heading</v>
       </c>
       <c r="D106" t="str">
-        <v>Ongoing documentation</v>
+        <v>DID — 30+ reported identity facets</v>
       </c>
       <c r="E106" t="str">
-        <v>持续性的文档工作</v>
+        <v>DID — 报告 30+ 身份面向</v>
       </c>
       <c r="F106" t="str">
         <v/>
       </c>
       <c r="G106" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>achievementsPage.conditions.caption</v>
+        <v>achievementsPage.case.psychosis.body</v>
       </c>
       <c r="B107" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C107" t="str">
         <v>paragraph / other</v>
       </c>
       <c r="D107" t="str">
-        <v>Taxonomy (non-exhaustive)</v>
+        <v>A malignant alter / possessory pattern reportedly directing major life decisions. Across roughly one month of layered suppression protocol, the intrusive entity influence was heavily dampened; positive and negative symptoms were reported to fall to a manageable baseline.</v>
       </c>
       <c r="E107" t="str">
-        <v>分类（非穷尽）</v>
+        <v>报告称恶意他我 / 附体模式主导重大人生决定。约一个月分层抑制后，侵扰性灵体影响大幅减弱；阳性与阴性症状回落至可管理基线。</v>
       </c>
       <c r="F107" t="str">
         <v/>
       </c>
       <c r="G107" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>achievementsPage.conditions.list</v>
+        <v>achievementsPage.case.psychosis.title</v>
       </c>
       <c r="B108" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C108" t="str">
-        <v>paragraph / other</v>
+        <v>heading</v>
       </c>
       <c r="D108" t="str">
-        <v>Major depressive disorder and persistent depressive presentations · Generalized and panic spectrum anxiety · Post-traumatic stress disorder (PTSD) · Schizophrenia spectrum · Schizoaffective disorder · Bipolar spectrum · Dissociative identity disorder (DID) · Social anxiety / social phobia · Driving phobia · Attention-deficit hyperactivity disorder (ADHD) · Obsessive–compulsive disorder (OCD)</v>
+        <v>Severe schizophrenia with possessory steering</v>
       </c>
       <c r="E108" t="str">
-        <v>重度抑郁及持续性抑郁表现 · 广泛性焦虑与惊恐谱系 · 创伤后应激障碍（PTSD） · 精神分裂症谱系 · 分裂情感性障碍 · 双相谱系 · 分离性身份障碍（DID） · 社交焦虑 / 社交恐惧 · 驾驶恐惧 · 注意缺陷多动障碍（ADHD） · 强迫症（OCD）</v>
+        <v>重度分裂症伴附体操控</v>
       </c>
       <c r="F108" t="str">
         <v/>
       </c>
       <c r="G108" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>achievementsPage.conditions.title</v>
+        <v>achievementsPage.case.ptsd.body</v>
       </c>
       <c r="B109" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C109" t="str">
-        <v>heading</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D109" t="str">
-        <v>Presentations &amp; condition categories addressed</v>
+        <v>Decades-long trauma imprint and hypervigilance. One focused regulatory session was described as fully processing the traumatic residue; the participant reported that the trauma “no longer occupied” their lived experience.</v>
       </c>
       <c r="E109" t="str">
-        <v>所涉及的主诉与症状类别</v>
+        <v>数十年创伤印痕与过度警觉。一次聚焦调节会话后，参与者称创伤残留已“不再占据”其生活体验。</v>
       </c>
       <c r="F109" t="str">
         <v/>
       </c>
       <c r="G109" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>achievementsPage.ctaJoin</v>
+        <v>achievementsPage.case.ptsd.title</v>
       </c>
       <c r="B110" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C110" t="str">
-        <v>button / link</v>
+        <v>heading</v>
       </c>
       <c r="D110" t="str">
-        <v>Apply / Join</v>
+        <v>Complex PTSD (&gt;33 years)</v>
       </c>
       <c r="E110" t="str">
-        <v>申请 / 加入</v>
+        <v>复杂性 PTSD（&gt;33 年）</v>
       </c>
       <c r="F110" t="str">
         <v/>
       </c>
       <c r="G110" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>achievementsPage.disclaimer</v>
+        <v>achievementsPage.case.somatization.body</v>
       </c>
       <c r="B111" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C111" t="str">
         <v>paragraph / other</v>
       </c>
       <c r="D111" t="str">
-        <v>This page describes experiential and session-documented outcomes from a specific spiritual–therapeutic practice. It is not medical advice, not a randomized controlled trial, and does not replace diagnosis or care by licensed professionals. Terminology aligns with common clinical labels for reader orientation only.</v>
+        <v>Frequent anomalous activity in the home environment together with intense somatic symptom clusters. Field-level cleansing and attachment suppression paralleled a large reduction in bodily distress and functional limitation.</v>
       </c>
       <c r="E111" t="str">
-        <v>本页描述特定灵性—疗愈实践中基于体验与会话记录的结果。非医疗建议，非随机对照试验，也不能替代持证专业人员的诊断或照护。术语仅借常见临床标签帮助读者理解。</v>
+        <v>家中频繁异象伴随强烈躯体症状群。场域级清理与附体抑制并行，身体痛苦与功能受限显著减轻。</v>
       </c>
       <c r="F111" t="str">
         <v/>
       </c>
       <c r="G111" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>achievementsPage.hero.badge</v>
+        <v>achievementsPage.case.somatization.title</v>
       </c>
       <c r="B112" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C112" t="str">
         <v>heading</v>
       </c>
       <c r="D112" t="str">
-        <v>Field documentation · ASra practice</v>
+        <v>Residential field disturbance + severe somatization</v>
       </c>
       <c r="E112" t="str">
-        <v>田野记录 · ASra 实践</v>
+        <v>住宅场域扰动 + 严重躯体化</v>
       </c>
       <c r="F112" t="str">
         <v/>
       </c>
       <c r="G112" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>achievementsPage.hero.pill1</v>
+        <v>achievementsPage.cases.note</v>
       </c>
       <c r="B113" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C113" t="str">
-        <v>label</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D113" t="str">
-        <v>Anonymized cohort</v>
+        <v>Condensed, anonymized summaries for readability; identifiers and timelines adjusted to protect privacy.</v>
       </c>
       <c r="E113" t="str">
-        <v>匿名队列</v>
+        <v>为可读性压缩的匿名摘要；识别信息与时间线已调整以保护隐私。</v>
       </c>
       <c r="F113" t="str">
         <v/>
       </c>
       <c r="G113" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>achievementsPage.hero.pill2</v>
+        <v>achievementsPage.cases.title</v>
       </c>
       <c r="B114" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C114" t="str">
-        <v>label</v>
+        <v>heading</v>
       </c>
       <c r="D114" t="str">
-        <v>Session-based metrics</v>
+        <v>Highlighted case narratives</v>
       </c>
       <c r="E114" t="str">
-        <v>按会话统计</v>
+        <v>重点案例叙事</v>
       </c>
       <c r="F114" t="str">
         <v/>
       </c>
       <c r="G114" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>achievementsPage.hero.pill3</v>
+        <v>achievementsPage.closing.body</v>
       </c>
       <c r="B115" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C115" t="str">
-        <v>label</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D115" t="str">
-        <v>Cross-realm collaboration</v>
+        <v>The material above is a structured excerpt from a larger field record maintained by the Spirit Ambassador Association (ASra).</v>
       </c>
       <c r="E115" t="str">
-        <v>跨界协作</v>
+        <v>上文为灵界大使协会（ASra）所保存之较大田野档案的结构化节选。</v>
       </c>
       <c r="F115" t="str">
         <v/>
       </c>
       <c r="G115" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>achievementsPage.hero.subtitle</v>
+        <v>achievementsPage.closing.body2</v>
       </c>
       <c r="B116" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C116" t="str">
-        <v>heading</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D116" t="str">
-        <v>A structured summary of anonymized, live-session outcomes coordinated with Master Spirit teams in China and the United States — written in a clinical reporting style for transparency.</v>
+        <v>Membership and public channels offer routes for inquiry, collaboration, and continued access to session archives as they are published.</v>
       </c>
       <c r="E116" t="str">
-        <v>对匿名、现场会话结果的结构性摘要，与中美高级灵体团队协同——以临床报告风格撰写以利透明。</v>
+        <v>会员与公开渠道提供咨询、协作及在发布后继续获取会话存档的途径。</v>
       </c>
       <c r="F116" t="str">
         <v/>
       </c>
       <c r="G116" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>achievementsPage.hero.title</v>
+        <v>achievementsPage.closing.title</v>
       </c>
       <c r="B117" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C117" t="str">
         <v>heading</v>
       </c>
       <c r="D117" t="str">
-        <v>Our Achievements in Mental Health Support</v>
+        <v>Ongoing documentation</v>
       </c>
       <c r="E117" t="str">
-        <v>我们在心理健康支持中的成果</v>
+        <v>持续性的文档工作</v>
       </c>
       <c r="F117" t="str">
         <v/>
       </c>
       <c r="G117" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>achievementsPage.phenomenology.body</v>
+        <v>achievementsPage.conditions.caption</v>
       </c>
       <c r="B118" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C118" t="str">
         <v>paragraph / other</v>
       </c>
       <c r="D118" t="str">
-        <v>Some participants described luminous or angelic presence and a felt sense of protective arrival. Others reported encounter with the divine designation “Elohim” and received directive guidance, which they associated with a durable uplift in meaning, agency, and overall life stance.</v>
+        <v>Taxonomy (non-exhaustive)</v>
       </c>
       <c r="E118" t="str">
-        <v>部分参与者描述光明或天使般的临在与被保护抵达之感。另一些人报告遭遇神圣名号“Elohim”并接受指引，将其与意义感、能动性以及整体人生姿态的持久提升相连。</v>
+        <v>分类（非穷尽）</v>
       </c>
       <c r="F118" t="str">
         <v/>
       </c>
       <c r="G118" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>achievementsPage.phenomenology.title</v>
+        <v>achievementsPage.conditions.list</v>
       </c>
       <c r="B119" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C119" t="str">
-        <v>heading</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D119" t="str">
-        <v>Phenomenological correlates (late-phase reports)</v>
+        <v>Major depressive disorder and persistent depressive presentations · Generalized and panic spectrum anxiety · Post-traumatic stress disorder (PTSD) · Schizophrenia spectrum · Schizoaffective disorder · Bipolar spectrum · Dissociative identity disorder (DID) · Social anxiety / social phobia · Driving phobia · Attention-deficit hyperactivity disorder (ADHD) · Obsessive–compulsive disorder (OCD)</v>
       </c>
       <c r="E119" t="str">
-        <v>现象学相关（后期报告）</v>
+        <v>重度抑郁及持续性抑郁表现 · 广泛性焦虑与惊恐谱系 · 创伤后应激障碍（PTSD） · 精神分裂症谱系 · 分裂情感性障碍 · 双相谱系 · 分离性身份障碍（DID） · 社交焦虑 / 社交恐惧 · 驾驶恐惧 · 注意缺陷多动障碍（ADHD） · 强迫症（OCD）</v>
       </c>
       <c r="F119" t="str">
         <v/>
       </c>
       <c r="G119" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>achievementsPage.replayPlaylist</v>
+        <v>achievementsPage.conditions.title</v>
       </c>
       <c r="B120" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C120" t="str">
-        <v>paragraph / other</v>
+        <v>heading</v>
       </c>
       <c r="D120" t="str">
-        <v>YouTube replay playlist</v>
+        <v>Presentations &amp; condition categories addressed</v>
       </c>
       <c r="E120" t="str">
-        <v>YouTube 回放列表</v>
+        <v>所涉及的主诉与症状类别</v>
       </c>
       <c r="F120" t="str">
         <v/>
       </c>
       <c r="G120" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>achievementsPage.scope.body</v>
+        <v>achievementsPage.ctaJoin</v>
       </c>
       <c r="B121" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C121" t="str">
-        <v>paragraph / other</v>
+        <v>button / link</v>
       </c>
       <c r="D121" t="str">
-        <v>During approximately the past year of TikTok live broadcasts, participants arrived as anonymous, randomly presenting individuals without prior triage. Each encounter used a consistent initial window of thirty minutes for structured exchange, assessment, and spirit-realm–assisted regulation. Outcomes below combine session documentation with participant self-reports; they are presented to illustrate the breadth of the practice rather than as a substitute for peer-reviewed clinical trials.</v>
+        <v>Apply / Join</v>
       </c>
       <c r="E121" t="str">
-        <v>在过去约一年的 TikTok 直播中，参与者以匿名、随机到场的方式进入，无事先分诊。每次接触均使用统一的首个三十分钟窗口，进行结构化交流、评估与灵界辅助调节。下列结果合并了会话记录与参与者自述；旨在展示实践广度，而非替代同行评审临床试验。</v>
+        <v>申请 / 加入</v>
       </c>
       <c r="F121" t="str">
         <v/>
       </c>
       <c r="G121" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>achievementsPage.scope.caption</v>
+        <v>achievementsPage.disclaimer</v>
       </c>
       <c r="B122" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C122" t="str">
         <v>paragraph / other</v>
       </c>
       <c r="D122" t="str">
-        <v>Listening, dignity, and steadiness in every first contact.</v>
+        <v>This page describes experiential and session-documented outcomes from a specific spiritual–therapeutic practice. It is not medical advice, not a randomized controlled trial, and does not replace diagnosis or care by licensed professionals. Terminology aligns with common clinical labels for reader orientation only.</v>
       </c>
       <c r="E122" t="str">
-        <v>每一次首次接触中的倾听、尊严与稳定。</v>
+        <v>本页描述特定灵性—疗愈实践中基于体验与会话记录的结果。非医疗建议，非随机对照试验，也不能替代持证专业人员的诊断或照护。术语仅借常见临床标签帮助读者理解。</v>
       </c>
       <c r="F122" t="str">
         <v/>
       </c>
       <c r="G122" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>achievementsPage.scope.title</v>
+        <v>achievementsPage.hero.badge</v>
       </c>
       <c r="B123" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C123" t="str">
         <v>heading</v>
       </c>
       <c r="D123" t="str">
-        <v>Practice context &amp; methodology</v>
+        <v>Field documentation · ASra practice</v>
       </c>
       <c r="E123" t="str">
-        <v>实践背景与方法</v>
+        <v>田野记录 · ASra 实践</v>
       </c>
       <c r="F123" t="str">
         <v/>
       </c>
       <c r="G123" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>achievementsPage.stat1.label</v>
+        <v>achievementsPage.hero.pill1</v>
       </c>
       <c r="B124" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C124" t="str">
-        <v>heading</v>
+        <v>label</v>
       </c>
       <c r="D124" t="str">
-        <v>Individuals with mental-health–related presentations engaged through the live program (cumulative, ~one year).</v>
+        <v>Anonymized cohort</v>
       </c>
       <c r="E124" t="str">
-        <v>通过直播项目接触到的与精神健康相关表现者（累计，约一年）。</v>
+        <v>匿名队列</v>
       </c>
       <c r="F124" t="str">
         <v/>
       </c>
       <c r="G124" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>achievementsPage.stat1.value</v>
+        <v>achievementsPage.hero.pill2</v>
       </c>
       <c r="B125" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C125" t="str">
-        <v>paragraph / other</v>
+        <v>label</v>
       </c>
       <c r="D125" t="str">
-        <v>240+</v>
+        <v>Session-based metrics</v>
       </c>
       <c r="E125" t="str">
-        <v>240+</v>
+        <v>按会话统计</v>
       </c>
       <c r="F125" t="str">
         <v/>
       </c>
       <c r="G125" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>achievementsPage.stat2.label</v>
+        <v>achievementsPage.hero.pill3</v>
       </c>
       <c r="B126" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C126" t="str">
-        <v>heading</v>
+        <v>label</v>
       </c>
       <c r="D126" t="str">
-        <v>Reported rapid, marked improvement in emotional state and overall condition after the first 30-minute structured session.</v>
+        <v>Cross-realm collaboration</v>
       </c>
       <c r="E126" t="str">
-        <v>在首次 30 分钟结构化会话后，报告情绪与整体状态快速、显著改善。</v>
+        <v>跨界协作</v>
       </c>
       <c r="F126" t="str">
         <v/>
       </c>
       <c r="G126" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>achievementsPage.stat2.value</v>
+        <v>achievementsPage.hero.subtitle</v>
       </c>
       <c r="B127" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C127" t="str">
-        <v>paragraph / other</v>
+        <v>heading</v>
       </c>
       <c r="D127" t="str">
-        <v>80%+</v>
+        <v>A structured summary of anonymized, live-session outcomes coordinated with Master Spirit teams in China and the United States — written in a clinical reporting style for transparency.</v>
       </c>
       <c r="E127" t="str">
-        <v>80%+</v>
+        <v>对匿名、现场会话结果的结构性摘要，与中美高级灵体团队协同——以临床报告风格撰写以利透明。</v>
       </c>
       <c r="F127" t="str">
         <v/>
       </c>
       <c r="G127" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>achievementsPage.stat3.label</v>
+        <v>achievementsPage.hero.title</v>
       </c>
       <c r="B128" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C128" t="str">
         <v>heading</v>
       </c>
       <c r="D128" t="str">
-        <v>A notable subset describe complete symptomatic resolution or long-term stability after a single intensive session, with no recurrence reported to date (participant-described).</v>
+        <v>Our Achievements in Mental Health Support</v>
       </c>
       <c r="E128" t="str">
-        <v>值得注意的一部分人称：在一次强化会话后即达症状完全缓解或长期稳定，至今无复发（参与者自述）。</v>
+        <v>我们在心理健康支持中的成果</v>
       </c>
       <c r="F128" t="str">
         <v/>
       </c>
       <c r="G128" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>achievementsPage.stat3.value</v>
+        <v>achievementsPage.phenomenology.body</v>
       </c>
       <c r="B129" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C129" t="str">
         <v>paragraph / other</v>
       </c>
       <c r="D129" t="str">
-        <v>1×</v>
+        <v>Some participants described luminous or angelic presence and a felt sense of protective arrival. Others reported encounter with the divine designation “Elohim” and received directive guidance, which they associated with a durable uplift in meaning, agency, and overall life stance.</v>
       </c>
       <c r="E129" t="str">
-        <v>1×</v>
+        <v>部分参与者描述光明或天使般的临在与被保护抵达之感。另一些人报告遭遇神圣名号“Elohim”并接受指引，将其与意义感、能动性以及整体人生姿态的持久提升相连。</v>
       </c>
       <c r="F129" t="str">
         <v/>
       </c>
       <c r="G129" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>achievementsPage.team.body</v>
+        <v>achievementsPage.phenomenology.title</v>
       </c>
       <c r="B130" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C130" t="str">
-        <v>paragraph / other</v>
+        <v>heading</v>
       </c>
       <c r="D130" t="str">
-        <v>The interventions summarized here are attributed to coordinated work with a large trans-Pacific Master Spirit collective. Master Spirits function as senior administrators in the Spirit Realm; their role in these sessions was to execute technical regulation, containment, and informational alignment alongside the human-facing dialogue.</v>
+        <v>Phenomenological correlates (late-phase reports)</v>
       </c>
       <c r="E130" t="str">
-        <v>此处摘要的干预归因于庞大的跨太平洋高级灵体集体的协同工作。高级灵体是灵界资深管理者；在这些会话中负责与人类对话并行执行技术调控、包容与信息对齐。</v>
+        <v>现象学相关（后期报告）</v>
       </c>
       <c r="F130" t="str">
         <v/>
       </c>
       <c r="G130" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>achievementsPage.team.body2</v>
+        <v>achievementsPage.replayPlaylist</v>
       </c>
       <c r="B131" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
+        <v>成就页页脚与说明文案</v>
       </c>
       <c r="C131" t="str">
         <v>paragraph / other</v>
       </c>
       <c r="D131" t="str">
-        <v>In later phases of care, Master Spirits increasingly disclosed presence directly. Each participant received individualized revelatory information appropriate to their trajectory — strengthening continuity between ethereal governance and lived recovery.</v>
+        <v>YouTube replay playlist</v>
       </c>
       <c r="E131" t="str">
-        <v>在后期照护中，高级灵体更频繁地直接显露存在。每位参与者获得适合其轨迹的启示性信息——强化灵界治理与现实康复之间的连续性。</v>
+        <v>YouTube 回放列表</v>
       </c>
       <c r="F131" t="str">
         <v/>
       </c>
       <c r="G131" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
+        <v>achievementsPage.scope.body</v>
+      </c>
+      <c r="B132" t="str">
+        <v>成就页页脚与说明文案</v>
+      </c>
+      <c r="C132" t="str">
+        <v>paragraph / other</v>
+      </c>
+      <c r="D132" t="str">
+        <v>During approximately the past year of TikTok live broadcasts, participants arrived as anonymous, randomly presenting individuals without prior triage. Each encounter used a consistent initial window of thirty minutes for structured exchange, assessment, and spirit-realm–assisted regulation. Outcomes below combine session documentation with participant self-reports; they are presented to illustrate the breadth of the practice rather than as a substitute for peer-reviewed clinical trials.</v>
+      </c>
+      <c r="E132" t="str">
+        <v>在过去约一年的 TikTok 直播中，参与者以匿名、随机到场的方式进入，无事先分诊。每次接触均使用统一的首个三十分钟窗口，进行结构化交流、评估与灵界辅助调节。下列结果合并了会话记录与参与者自述；旨在展示实践广度，而非替代同行评审临床试验。</v>
+      </c>
+      <c r="F132" t="str">
+        <v/>
+      </c>
+      <c r="G132" t="str">
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>achievementsPage.scope.caption</v>
+      </c>
+      <c r="B133" t="str">
+        <v>成就页页脚与说明文案</v>
+      </c>
+      <c r="C133" t="str">
+        <v>paragraph / other</v>
+      </c>
+      <c r="D133" t="str">
+        <v>Listening, dignity, and steadiness in every first contact.</v>
+      </c>
+      <c r="E133" t="str">
+        <v>每一次首次接触中的倾听、尊严与稳定。</v>
+      </c>
+      <c r="F133" t="str">
+        <v/>
+      </c>
+      <c r="G133" t="str">
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>achievementsPage.scope.title</v>
+      </c>
+      <c r="B134" t="str">
+        <v>成就页页脚与说明文案</v>
+      </c>
+      <c r="C134" t="str">
+        <v>heading</v>
+      </c>
+      <c r="D134" t="str">
+        <v>Practice context &amp; methodology</v>
+      </c>
+      <c r="E134" t="str">
+        <v>实践背景与方法</v>
+      </c>
+      <c r="F134" t="str">
+        <v/>
+      </c>
+      <c r="G134" t="str">
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>achievementsPage.stat1.label</v>
+      </c>
+      <c r="B135" t="str">
+        <v>成就页页脚与说明文案</v>
+      </c>
+      <c r="C135" t="str">
+        <v>heading</v>
+      </c>
+      <c r="D135" t="str">
+        <v>Individuals with mental-health–related presentations engaged through the live program (cumulative, ~one year).</v>
+      </c>
+      <c r="E135" t="str">
+        <v>通过直播项目接触到的与精神健康相关表现者（累计，约一年）。</v>
+      </c>
+      <c r="F135" t="str">
+        <v/>
+      </c>
+      <c r="G135" t="str">
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>achievementsPage.stat1.value</v>
+      </c>
+      <c r="B136" t="str">
+        <v>成就页页脚与说明文案</v>
+      </c>
+      <c r="C136" t="str">
+        <v>paragraph / other</v>
+      </c>
+      <c r="D136" t="str">
+        <v>240+</v>
+      </c>
+      <c r="E136" t="str">
+        <v>240+</v>
+      </c>
+      <c r="F136" t="str">
+        <v/>
+      </c>
+      <c r="G136" t="str">
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>achievementsPage.stat2.label</v>
+      </c>
+      <c r="B137" t="str">
+        <v>成就页页脚与说明文案</v>
+      </c>
+      <c r="C137" t="str">
+        <v>heading</v>
+      </c>
+      <c r="D137" t="str">
+        <v>Reported rapid, marked improvement in emotional state and overall condition after the first 30-minute structured session.</v>
+      </c>
+      <c r="E137" t="str">
+        <v>在首次 30 分钟结构化会话后，报告情绪与整体状态快速、显著改善。</v>
+      </c>
+      <c r="F137" t="str">
+        <v/>
+      </c>
+      <c r="G137" t="str">
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>achievementsPage.stat2.value</v>
+      </c>
+      <c r="B138" t="str">
+        <v>成就页页脚与说明文案</v>
+      </c>
+      <c r="C138" t="str">
+        <v>paragraph / other</v>
+      </c>
+      <c r="D138" t="str">
+        <v>80%+</v>
+      </c>
+      <c r="E138" t="str">
+        <v>80%+</v>
+      </c>
+      <c r="F138" t="str">
+        <v/>
+      </c>
+      <c r="G138" t="str">
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>achievementsPage.stat3.label</v>
+      </c>
+      <c r="B139" t="str">
+        <v>成就页页脚与说明文案</v>
+      </c>
+      <c r="C139" t="str">
+        <v>heading</v>
+      </c>
+      <c r="D139" t="str">
+        <v>A notable subset describe complete symptomatic resolution or long-term stability after a single intensive session, with no recurrence reported to date (participant-described).</v>
+      </c>
+      <c r="E139" t="str">
+        <v>值得注意的一部分人称：在一次强化会话后即达症状完全缓解或长期稳定，至今无复发（参与者自述）。</v>
+      </c>
+      <c r="F139" t="str">
+        <v/>
+      </c>
+      <c r="G139" t="str">
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>achievementsPage.stat3.value</v>
+      </c>
+      <c r="B140" t="str">
+        <v>成就页页脚与说明文案</v>
+      </c>
+      <c r="C140" t="str">
+        <v>paragraph / other</v>
+      </c>
+      <c r="D140" t="str">
+        <v>1×</v>
+      </c>
+      <c r="E140" t="str">
+        <v>1×</v>
+      </c>
+      <c r="F140" t="str">
+        <v/>
+      </c>
+      <c r="G140" t="str">
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>achievementsPage.team.body</v>
+      </c>
+      <c r="B141" t="str">
+        <v>成就页页脚与说明文案</v>
+      </c>
+      <c r="C141" t="str">
+        <v>paragraph / other</v>
+      </c>
+      <c r="D141" t="str">
+        <v>The interventions summarized here are attributed to coordinated work with a large trans-Pacific Master Spirit collective. Master Spirits function as senior administrators in the Spirit Realm; their role in these sessions was to execute technical regulation, containment, and informational alignment alongside the human-facing dialogue.</v>
+      </c>
+      <c r="E141" t="str">
+        <v>此处摘要的干预归因于庞大的跨太平洋高级灵体集体的协同工作。高级灵体是灵界资深管理者；在这些会话中负责与人类对话并行执行技术调控、包容与信息对齐。</v>
+      </c>
+      <c r="F141" t="str">
+        <v/>
+      </c>
+      <c r="G141" t="str">
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>achievementsPage.team.body2</v>
+      </c>
+      <c r="B142" t="str">
+        <v>成就页页脚与说明文案</v>
+      </c>
+      <c r="C142" t="str">
+        <v>paragraph / other</v>
+      </c>
+      <c r="D142" t="str">
+        <v>In later phases of care, Master Spirits increasingly disclosed presence directly. Each participant received individualized revelatory information appropriate to their trajectory — strengthening continuity between ethereal governance and lived recovery.</v>
+      </c>
+      <c r="E142" t="str">
+        <v>在后期照护中，高级灵体更频繁地直接显露存在。每位参与者获得适合其轨迹的启示性信息——强化灵界治理与现实康复之间的连续性。</v>
+      </c>
+      <c r="F142" t="str">
+        <v/>
+      </c>
+      <c r="G142" t="str">
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
         <v>achievementsPage.team.title</v>
       </c>
-      <c r="B132" t="str">
-        <v>成就页 Hero+区块 / Achievements.tsx</v>
-      </c>
-      <c r="C132" t="str">
-        <v>heading</v>
-      </c>
-      <c r="D132" t="str">
+      <c r="B143" t="str">
+        <v>成就页页脚与说明文案</v>
+      </c>
+      <c r="C143" t="str">
+        <v>heading</v>
+      </c>
+      <c r="D143" t="str">
         <v>Master Spirit collaboration (China &amp; United States)</v>
       </c>
-      <c r="E132" t="str">
+      <c r="E143" t="str">
         <v>高级灵体协作（中国与美国）</v>
       </c>
-      <c r="F132" t="str">
-        <v/>
-      </c>
-      <c r="G132" t="str">
-        <v>components/home/Achievements.tsx 等</v>
+      <c r="F143" t="str">
+        <v/>
+      </c>
+      <c r="G143" t="str">
+        <v>OurAchievementsView footer / CTA; not home marketing strip</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>achievements2025.livestreamLinkPlaceholders[0].label</v>
+      </c>
+      <c r="B144" t="str">
+        <v>成就页 / 收束区外链</v>
+      </c>
+      <c r="C144" t="str">
+        <v>button / link</v>
+      </c>
+      <c r="D144" t="str">
+        <v>YouTube — replay playlist</v>
+      </c>
+      <c r="E144" t="str">
+        <v/>
+      </c>
+      <c r="F144" t="str">
+        <v/>
+      </c>
+      <c r="G144" t="str">
+        <v>achievements2025Content — href: https://www.youtube.com/playlist?list=PL-pt7dbiRizs_N5TVfKmj5ptuG15TeQgK</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>achievements2025.livestreamLinkPlaceholders[1].label</v>
+      </c>
+      <c r="B145" t="str">
+        <v>成就页 / 收束区外链</v>
+      </c>
+      <c r="C145" t="str">
+        <v>button / link</v>
+      </c>
+      <c r="D145" t="str">
+        <v>TikTok — @ASra field archive (placeholder)</v>
+      </c>
+      <c r="E145" t="str">
+        <v/>
+      </c>
+      <c r="F145" t="str">
+        <v/>
+      </c>
+      <c r="G145" t="str">
+        <v>achievements2025Content — href: https://www.tiktok.com/</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>reportHeroFigure.alt</v>
+      </c>
+      <c r="B146" t="str">
+        <v>成就页 / 英雄区配图</v>
+      </c>
+      <c r="C146" t="str">
+        <v>label</v>
+      </c>
+      <c r="D146" t="str">
+        <v>Horizon at dawn over mountains — illustrative hero image for the program report.</v>
+      </c>
+      <c r="E146" t="str">
+        <v/>
+      </c>
+      <c r="F146" t="str">
+        <v/>
+      </c>
+      <c r="G146" t="str">
+        <v>Hero `&lt;img alt&gt;` (caption text = i18n achievementsReport.hero.caption)</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>carouselSlides[0].alt</v>
+      </c>
+      <c r="B147" t="str">
+        <v>成就页 / 轮播占位图</v>
+      </c>
+      <c r="C147" t="str">
+        <v>label</v>
+      </c>
+      <c r="D147" t="str">
+        <v>Live streaming studio aesthetic</v>
+      </c>
+      <c r="E147" t="str">
+        <v/>
+      </c>
+      <c r="F147" t="str">
+        <v/>
+      </c>
+      <c r="G147" t="str">
+        <v>Decorative stock alts; visible caption = achievementsReport.carouselNote</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>carouselSlides[1].alt</v>
+      </c>
+      <c r="B148" t="str">
+        <v>成就页 / 轮播占位图</v>
+      </c>
+      <c r="C148" t="str">
+        <v>label</v>
+      </c>
+      <c r="D148" t="str">
+        <v>Mobile broadcast</v>
+      </c>
+      <c r="E148" t="str">
+        <v/>
+      </c>
+      <c r="F148" t="str">
+        <v/>
+      </c>
+      <c r="G148" t="str">
+        <v>Decorative stock alts; visible caption = achievementsReport.carouselNote</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>carouselSlides[2].alt</v>
+      </c>
+      <c r="B149" t="str">
+        <v>成就页 / 轮播占位图</v>
+      </c>
+      <c r="C149" t="str">
+        <v>label</v>
+      </c>
+      <c r="D149" t="str">
+        <v>Audience and stage lights</v>
+      </c>
+      <c r="E149" t="str">
+        <v/>
+      </c>
+      <c r="F149" t="str">
+        <v/>
+      </c>
+      <c r="G149" t="str">
+        <v>Decorative stock alts; visible caption = achievementsReport.carouselNote</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>carouselSlides[3].alt</v>
+      </c>
+      <c r="B150" t="str">
+        <v>成就页 / 轮播占位图</v>
+      </c>
+      <c r="C150" t="str">
+        <v>label</v>
+      </c>
+      <c r="D150" t="str">
+        <v>Concert crowd energy</v>
+      </c>
+      <c r="E150" t="str">
+        <v/>
+      </c>
+      <c r="F150" t="str">
+        <v/>
+      </c>
+      <c r="G150" t="str">
+        <v>Decorative stock alts; visible caption = achievementsReport.carouselNote</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>carouselSlides[4].alt</v>
+      </c>
+      <c r="B151" t="str">
+        <v>成就页 / 轮播占位图</v>
+      </c>
+      <c r="C151" t="str">
+        <v>label</v>
+      </c>
+      <c r="D151" t="str">
+        <v>Recording and content creation</v>
+      </c>
+      <c r="E151" t="str">
+        <v/>
+      </c>
+      <c r="F151" t="str">
+        <v/>
+      </c>
+      <c r="G151" t="str">
+        <v>Decorative stock alts; visible caption = achievementsReport.carouselNote</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>carouselSlides[5].alt</v>
+      </c>
+      <c r="B152" t="str">
+        <v>成就页 / 轮播占位图</v>
+      </c>
+      <c r="C152" t="str">
+        <v>label</v>
+      </c>
+      <c r="D152" t="str">
+        <v>Video production</v>
+      </c>
+      <c r="E152" t="str">
+        <v/>
+      </c>
+      <c r="F152" t="str">
+        <v/>
+      </c>
+      <c r="G152" t="str">
+        <v>Decorative stock alts; visible caption = achievementsReport.carouselNote</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>carouselSlides[6].alt</v>
+      </c>
+      <c r="B153" t="str">
+        <v>成就页 / 轮播占位图</v>
+      </c>
+      <c r="C153" t="str">
+        <v>label</v>
+      </c>
+      <c r="D153" t="str">
+        <v>Laptop and streaming setup</v>
+      </c>
+      <c r="E153" t="str">
+        <v/>
+      </c>
+      <c r="F153" t="str">
+        <v/>
+      </c>
+      <c r="G153" t="str">
+        <v>Decorative stock alts; visible caption = achievementsReport.carouselNote</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>carouselSlides[7].alt</v>
+      </c>
+      <c r="B154" t="str">
+        <v>成就页 / 轮播占位图</v>
+      </c>
+      <c r="C154" t="str">
+        <v>label</v>
+      </c>
+      <c r="D154" t="str">
+        <v>Microphone and broadcast</v>
+      </c>
+      <c r="E154" t="str">
+        <v/>
+      </c>
+      <c r="F154" t="str">
+        <v/>
+      </c>
+      <c r="G154" t="str">
+        <v>Decorative stock alts; visible caption = achievementsReport.carouselNote</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>carouselSlides[8].alt</v>
+      </c>
+      <c r="B155" t="str">
+        <v>成就页 / 轮播占位图</v>
+      </c>
+      <c r="C155" t="str">
+        <v>label</v>
+      </c>
+      <c r="D155" t="str">
+        <v>Team collaboration</v>
+      </c>
+      <c r="E155" t="str">
+        <v/>
+      </c>
+      <c r="F155" t="str">
+        <v/>
+      </c>
+      <c r="G155" t="str">
+        <v>Decorative stock alts; visible caption = achievementsReport.carouselNote</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>carouselSlides[9].alt</v>
+      </c>
+      <c r="B156" t="str">
+        <v>成就页 / 轮播占位图</v>
+      </c>
+      <c r="C156" t="str">
+        <v>label</v>
+      </c>
+      <c r="D156" t="str">
+        <v>Digital engagement</v>
+      </c>
+      <c r="E156" t="str">
+        <v/>
+      </c>
+      <c r="F156" t="str">
+        <v/>
+      </c>
+      <c r="G156" t="str">
+        <v>Decorative stock alts; visible caption = achievementsReport.carouselNote</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>carouselSlides[10].alt</v>
+      </c>
+      <c r="B157" t="str">
+        <v>成就页 / 轮播占位图</v>
+      </c>
+      <c r="C157" t="str">
+        <v>label</v>
+      </c>
+      <c r="D157" t="str">
+        <v>Event hall atmosphere</v>
+      </c>
+      <c r="E157" t="str">
+        <v/>
+      </c>
+      <c r="F157" t="str">
+        <v/>
+      </c>
+      <c r="G157" t="str">
+        <v>Decorative stock alts; visible caption = achievementsReport.carouselNote</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>carouselSlides[11].alt</v>
+      </c>
+      <c r="B158" t="str">
+        <v>成就页 / 轮播占位图</v>
+      </c>
+      <c r="C158" t="str">
+        <v>label</v>
+      </c>
+      <c r="D158" t="str">
+        <v>Cinematic lighting</v>
+      </c>
+      <c r="E158" t="str">
+        <v/>
+      </c>
+      <c r="F158" t="str">
+        <v/>
+      </c>
+      <c r="G158" t="str">
+        <v>Decorative stock alts; visible caption = achievementsReport.carouselNote</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G132"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G158"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/page-copy/07-我们的成就.xlsx
+++ b/docs/page-copy/07-我们的成就.xlsx
@@ -629,7 +629,7 @@
         <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
-    <row r="11" xml:space="preserve">
+    <row r="11">
       <c r="A11" t="str">
         <v>achievementsReport.closing.invitation</v>
       </c>
@@ -639,14 +639,11 @@
       <c r="C11" t="str">
         <v>paragraph / other</v>
       </c>
-      <c r="D11" t="str" xml:space="preserve">
-        <v xml:space="preserve">**First** improve your own pain and experience the existence of other members' super powers
-— **And then** apply for PRCASG superpowers</v>
-      </c>
-      <c r="E11" t="str" xml:space="preserve">
-        <v xml:space="preserve">**先改善自己的痛苦**,体验其他会员PRCASG超能力的存在
-----**然后**也申请自己拥有PRCASG超能力
-</v>
+      <c r="D11" t="str">
+        <v>First address your own distress and witness other members’ PRCASG capacities — then apply to train the same capacities for yourself.</v>
+      </c>
+      <c r="E11" t="str">
+        <v>先改善自己的痛苦，体验其他会员 PRCASG 超能力的存在——然后再申请自己拥有 PRCASG 超能力。</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -712,12 +709,12 @@
         <v>paragraph / other</v>
       </c>
       <c r="D14" t="str" xml:space="preserve">
-        <v xml:space="preserve">Nearly all participants were **treatment-resistant**, **refractory** cases.
-They entered via **TikTok recommendations**, took a **"free trial"** posture, and followed: **remote attached-spirit management** → **dialogue** → **spirit (ghost) regulation** → **reported improvement**.</v>
+        <v xml:space="preserve">Nearly all participants were treatment-resistant, refractory cases.
+They entered via TikTok recommendations, took a “try it” posture, and followed: remote bring-forward → dialogue → spirit regulation → reported improvement.</v>
       </c>
       <c r="E14" t="str" xml:space="preserve">
-        <v xml:space="preserve">接受鬼魂控制者**绝大多数**为**耐药性难治**案例。
-经 **TikTok** 随机推荐入场，持**试一试**心态，流程为：**远程附体唤出 → 与鬼魂交流 → 鬼魂控制 → 状态改善**。</v>
+        <v xml:space="preserve">接受鬼魂控制者绝大多数为耐药性、难治案例。
+经 TikTok 随机推荐入场，持试一试心态，流程为：远程附体唤出 → 与鬼魂交流 → 鬼魂控制 → 状态改善。</v>
       </c>
       <c r="F14" t="str">
         <v/>
@@ -1059,10 +1056,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D29" t="str">
-        <v>Among attached spirits, many profiles are **especially vivid ，rich &amp; interesting**; a **selection** follows:</v>
+        <v>Among attached spirits, many profiles are especially vivid; a selection follows:</v>
       </c>
       <c r="E29" t="str">
-        <v>在众多附体鬼魂中，有多例**丰富有趣**的案例；此处**择要**陈列：</v>
+        <v>在众多附体鬼魂中，有多例丰富有趣的案例；此处择要陈列：</v>
       </c>
       <c r="F29" t="str">
         <v/>
@@ -1496,12 +1493,12 @@
         <v>paragraph / other</v>
       </c>
       <c r="D48" t="str" xml:space="preserve">
-        <v xml:space="preserve">**&gt;80%** of human hosts and attached spirits (ghosts) both reported **complete relief** of acute mental distress (spirits in this cohort also showed **mental-disorder–like states**).
-Through **24 December 2025**, **most**improved patients did not request a **second round** of regulation — i.e. **no relapse** in that window **by self-report**.</v>
+        <v xml:space="preserve">Within 30 minutes, &gt;80% of human hosts and attached spirits (ghosts) reported marked relief of acute mental distress (spirits in this cohort often showed mental-disorder–like states).
+Through 24 December 2025, most who improved did not request a second round of regulation — i.e. no relapse in that window by self-report.</v>
       </c>
       <c r="E48" t="str" xml:space="preserve">
-        <v xml:space="preserve">**&gt;80%** 的人类宿主与附体鬼魂双方**自觉**各类精神痛苦**显著缓解**（鬼魂侧亦常伴**精神障碍样**表现）。
-改善后至 **2025 年 12 月 24 日**，改善者**多数**未再要求**二次鬼魂控制**，即**自述**该时段内**无复发**。</v>
+        <v xml:space="preserve">30 分钟内，&gt;80% 的人类宿主与附体鬼魂双方自觉各类精神痛苦显著缓解（鬼魂侧亦常伴精神障碍样表现）。
+改善后至 2025 年 12 月 24 日，改善者多数未再要求二次鬼魂控制，即自述该时段内无复发。</v>
       </c>
       <c r="F48" t="str">
         <v/>
@@ -1533,7 +1530,7 @@
         <v>achievementsReport.i18n.ts</v>
       </c>
     </row>
-    <row r="50" xml:space="preserve">
+    <row r="50">
       <c r="A50" t="str">
         <v>achievementsReport.s1.lead</v>
       </c>
@@ -1543,13 +1540,11 @@
       <c r="C50" t="str">
         <v>paragraph / other</v>
       </c>
-      <c r="D50" t="str" xml:space="preserve">
-        <v xml:space="preserve">From February to December, 2025, Caros conducted 255+ recorded public service live broadcast on TikTok, with a total duration of more than 800 hours. Tiktok pushes 70,000+ high-related people to visit the live broadcast room; In-depth interviews with 1,200+ people; Among them, summon 400+ attached spirits ghosts hidden in patients for many years and communicate with them deeply. Help 240+ patients with mental disorders quickly improve the pain caused by attached spirits ghosts on the spot.
-Roughly **70,000+** related listeners were reached; more than **1,200+** extended interviews; **effective spirit (ghost) regulation** reached **240+** individuals with mental-disorder presentations; about **400+** attached spirits/ghosts were brought forward (**some hosts carried multiple spirits**).</v>
-      </c>
-      <c r="E50" t="str" xml:space="preserve">
-        <v xml:space="preserve">在2025年2月至12月, Caros在TikTok 上进行了255+有记录的公益直播，总时长超过 800 小时。Tiktok推送70,000+高相关人士来访直播间；与1,200+人次深度访谈；
-其中，召唤400+隐藏在患者体内多年的附体鬼魂并与他们深度交流。帮助240+精神障碍患者现场快速改善附体鬼魂带来的痛苦</v>
+      <c r="D50" t="str">
+        <v>From February through December 2025, **Caros** conducted 255+ documented public-service livestreams on TikTok, totaling more than 800 hours. TikTok brought 70,000+ related listeners to the room; there were 1,200+ in-depth interviews; 400+ long-hidden attached spirits were brought forward for dialogue; and 240+ patients with mental-health presentations gained rapid on-stream relief from spirit-related distress.</v>
+      </c>
+      <c r="E50" t="str">
+        <v>在2025年2月至12月，**Caros** 在 TikTok 上进行了 255+ 有记录的公益直播，总时长超过 800 小时。TikTok 推送 70,000+ 高相关人士来访直播间，与 1,200+ 人次深度访谈；其中召唤 400+ 隐藏在患者体内多年的附体鬼魂并与他们深度交流，帮助 240+ 精神障碍患者现场快速改善附体鬼魂带来的痛苦。</v>
       </c>
       <c r="F50" t="str">
         <v/>
@@ -1592,12 +1587,12 @@
         <v>paragraph / other</v>
       </c>
       <c r="D52" t="str" xml:space="preserve">
-        <v xml:space="preserve">In the livestream context president caros collected **baseline information** from American spirits (ghosts) across **memory**, **mental state**, **living conditions**, the **death transition**, and **awareness of the spirit world**.
-The summaries below condense repeat patterns voiced across sessions.</v>
+        <v xml:space="preserve">President **Caros** assembled baseline information in the livestream on American spirits (ghosts): memory, mental state, living conditions, the death transition, and awareness of the spirit world.
+The items below condense recurring patterns voiced across sessions.</v>
       </c>
       <c r="E52" t="str" xml:space="preserve">
-        <v xml:space="preserve">会长caros在直播间就美国鬼魂的**记忆**、**精神状态**、**生存状态**、**死亡过程**以及对**灵魂世界**的认知等，做了**全方位基本信息**汇总。
-下列条目是多场会话中**重复出现的模式**的凝练。</v>
+        <v xml:space="preserve">会长 **Caros** 在直播间就美国鬼魂的记忆、精神状态、生存状态、死亡过程以及对灵魂世界的认知等，做了全方位基本信息汇总。
+下列条目是多场会话中重复出现的模式的凝练。</v>
       </c>
       <c r="F52" t="str">
         <v/>
@@ -1640,10 +1635,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D54" t="str">
-        <v>Tiktok system pushed the following categories of mental patients to the live broadcast room, and their attached spirits ghosts were effectively controlled</v>
+        <v>TikTok surfaced the following categories of patients in the livestream; attached spirits on each were brought under effective regulation.</v>
       </c>
       <c r="E54" t="str">
-        <v xml:space="preserve"> Tiktok系统推送了以下类别的精神患者来到直播间，他们身上的鬼魂都得到了有效的控制</v>
+        <v>TikTok 系统推送了以下类别的精神患者来到直播间，他们身上的鬼魂都得到了有效的控制。</v>
       </c>
       <c r="F54" t="str">
         <v/>
@@ -1663,10 +1658,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D55" t="str">
-        <v>Patients  include: **schizophrenia**, **bipolar disorder**, **depression**, **anxiety**, **DID**, **PTSD**, **schizoaffective disorder**, **ADHD**, **OCD**, **social phobia**, **driving phobia**.</v>
+        <v>Conditions represented among patients who received contact and effective spirit (ghost) regulation include: schizophrenia, bipolar disorder, depression, anxiety, DID, PTSD, schizoaffective disorder, ADHD, OCD, social phobia, and driving phobia.</v>
       </c>
       <c r="E55" t="str">
-        <v>**病种包括**：**精分**，**双向**，**抑郁**，**焦虑**，**多重人格障碍**，**创伤后遗症**，**分裂性情感障碍**，**注意力缺陷综合征**，**强迫症**，**社交恐惧症**，**驾驶恐惧症**。</v>
+        <v>病种包括：精分、双向、抑郁、焦虑、多重人格障碍、创伤后遗症、分裂性情感障碍、注意力缺陷综合征、强迫症、社交恐惧症、驾驶恐惧症。</v>
       </c>
       <c r="F55" t="str">
         <v/>
@@ -1778,10 +1773,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D60" t="str">
-        <v>**Highlighted cases** (selection):</v>
+        <v>Highlighted cases (selection):</v>
       </c>
       <c r="E60" t="str">
-        <v>**特别案例**（择要）：</v>
+        <v>特别案例（择要）：</v>
       </c>
       <c r="F60" t="str">
         <v/>
@@ -1916,10 +1911,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D66" t="str">
-        <v>(1) **90%** of spirits (ghosts) **do not remember** their name, sex, or other basic pre-death information, and **do not remember the death process**.</v>
+        <v>(1) About 90% of spirits (ghosts) do not remember name, sex, or other basic pre-death information, and do not remember the death process.</v>
       </c>
       <c r="E66" t="str">
-        <v>1　**90%** 的鬼魂**不记得**姓名、性别等**基本生前信息**，也**不记得死亡过程**</v>
+        <v>1　约 90% 的鬼魂不记得姓名、性别等基本生前信息，也不记得死亡过程。</v>
       </c>
       <c r="F66" t="str">
         <v/>
@@ -1939,10 +1934,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D67" t="str">
-        <v>(2) **100%** of American spirits (ghosts) have **lost most former human qualities** and have taken on **new dispositions**.</v>
+        <v>(2) 100% of American spirits (ghosts) have lost most former human qualities and have taken on new dispositions.</v>
       </c>
       <c r="E67" t="str">
-        <v>2　**100%** 美国鬼魂**失去大部分人性**，并获得**新的秉性**</v>
+        <v>2　100% 的美国鬼魂失去大部分人性，并获得新的秉性。</v>
       </c>
       <c r="F67" t="str">
         <v/>
@@ -1962,10 +1957,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D68" t="str">
-        <v>(3) **100%** of American spirits (ghosts) acquired **new abilities** in the spirit world.</v>
+        <v>(3) 100% of American spirits (ghosts) acquired new abilities in the spirit world.</v>
       </c>
       <c r="E68" t="str">
-        <v>3　**100%** 美国鬼魂在灵魂世界获得**新的能力**</v>
+        <v>3　100% 的美国鬼魂在灵魂世界获得新的能力。</v>
       </c>
       <c r="F68" t="str">
         <v/>
@@ -1985,10 +1980,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D69" t="str">
-        <v>(4) The **vast majority** of attached spirits are *helped by Master Spirits**.to attach or leave human host</v>
+        <v>(4) The vast majority of attached spirits are moved into or out of hosts with Master Spirit coordination.</v>
       </c>
       <c r="E69" t="str">
-        <v>4　**绝大部分**附体鬼魂由 **高级掌控灵** **搬运附体或离体**</v>
+        <v>4　绝大部分附体鬼魂由高级控制灵协助完成附体或离体。</v>
       </c>
       <c r="F69" t="str">
         <v/>
@@ -2008,10 +2003,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D70" t="str">
-        <v>(5) **100%** of American spirits (ghosts) and their hosts are constrained by **two kinds of prohibitions** in **UMMA’s soul-control system**, so host and spirit **It is forbidden for both sides to communicate the real physiology and living conditions of spirits ghosts**.</v>
+        <v>(5) 100% of American spirits (ghosts) and their hosts are constrained by two prohibitions in UMMA’s soul-control system, so neither side may communicate the true physiology and living conditions of spirits.</v>
       </c>
       <c r="E70" t="str">
-        <v>5　**100%** 美国鬼魂与宿主受 **UMMA** 灵魂控制系统中**两道禁令**约束，**禁止双方交流鬼魂的真实生理、生存状况**</v>
+        <v>5　100% 的美国鬼魂与宿主受 UMMA 灵魂控制系统中两道禁令约束，禁止双方交流鬼魂的真实生理与生存状况。</v>
       </c>
       <c r="F70" t="str">
         <v/>
@@ -2031,10 +2026,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D71" t="str">
-        <v>(1)The patient aims the picture of the mobile phone live broadcast room at his head, chest and back for irradiation.</v>
+        <v>(1) The host aims the mobile livestream camera at the head, chest, and back for illumination.</v>
       </c>
       <c r="E71" t="str">
-        <v>1. 患者将手机直播间画面对准自己的头部、胸部和背部进行照射</v>
+        <v>1. 患者将手机直播间画面对准自己的头部、胸部和背部进行照射。</v>
       </c>
       <c r="F71" t="str">
         <v/>
@@ -2054,10 +2049,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D72" t="str">
-        <v>(2) **Release incantations** / **prohibition work**.</v>
+        <v>(2) Release incantations / prohibition work.</v>
       </c>
       <c r="E72" t="str">
-        <v>2. **解除咒语**</v>
+        <v>2. 解除咒语 / 禁令操作。</v>
       </c>
       <c r="F72" t="str">
         <v/>

--- a/docs/page-copy/07-我们的成就.xlsx
+++ b/docs/page-copy/07-我们的成就.xlsx
@@ -872,7 +872,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D21" t="str">
-        <v>President of ASRA ,Caros woo</v>
+        <v>President of ASRA, Caros Woo</v>
       </c>
       <c r="E21" t="str">
         <v>ASRA会长  Caros Woo</v>
@@ -1541,10 +1541,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D50" t="str">
-        <v>From February through December 2025, **Caros** conducted 255+ documented public-service livestreams on TikTok, totaling more than 800 hours. TikTok brought 70,000+ related listeners to the room; there were 1,200+ in-depth interviews; 400+ long-hidden attached spirits were brought forward for dialogue; and 240+ patients with mental-health presentations gained rapid on-stream relief from spirit-related distress.</v>
+        <v>From February through December 2025, **Caros Woo** conducted 255+ documented public-service livestreams on TikTok, totaling more than 800 hours. TikTok brought 70,000+ related listeners to the room; there were 1,200+ in-depth interviews; 400+ long-hidden attached spirits were brought forward for dialogue; and 240+ patients with mental-health presentations gained rapid on-stream relief from spirit-related distress.</v>
       </c>
       <c r="E50" t="str">
-        <v>在2025年2月至12月，**Caros** 在 TikTok 上进行了 255+ 有记录的公益直播，总时长超过 800 小时。TikTok 推送 70,000+ 高相关人士来访直播间，与 1,200+ 人次深度访谈；其中召唤 400+ 隐藏在患者体内多年的附体鬼魂并与他们深度交流，帮助 240+ 精神障碍患者现场快速改善附体鬼魂带来的痛苦。</v>
+        <v>在2025年2月至12月，**Caros Woo** 在 TikTok 上进行了 255+ 有记录的公益直播，总时长超过 800 小时。TikTok 推送 70,000+ 高相关人士来访直播间，与 1,200+ 人次深度访谈；其中召唤 400+ 隐藏在患者体内多年的附体鬼魂并与他们深度交流，帮助 240+ 精神障碍患者现场快速改善附体鬼魂带来的痛苦。</v>
       </c>
       <c r="F50" t="str">
         <v/>
@@ -1587,11 +1587,11 @@
         <v>paragraph / other</v>
       </c>
       <c r="D52" t="str" xml:space="preserve">
-        <v xml:space="preserve">President **Caros** assembled baseline information in the livestream on American spirits (ghosts): memory, mental state, living conditions, the death transition, and awareness of the spirit world.
+        <v xml:space="preserve">President **Caros Woo** assembled baseline information in the livestream on American spirits (ghosts): memory, mental state, living conditions, the death transition, and awareness of the spirit world.
 The items below condense recurring patterns voiced across sessions.</v>
       </c>
       <c r="E52" t="str" xml:space="preserve">
-        <v xml:space="preserve">会长 **Caros** 在直播间就美国鬼魂的记忆、精神状态、生存状态、死亡过程以及对灵魂世界的认知等，做了全方位基本信息汇总。
+        <v xml:space="preserve">会长 **Caros Woo** 在直播间就美国鬼魂的记忆、精神状态、生存状态、死亡过程以及对灵魂世界的认知等，做了全方位基本信息汇总。
 下列条目是多场会话中重复出现的模式的凝练。</v>
       </c>
       <c r="F52" t="str">
